--- a/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2677_W0056F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.99185806890334</v>
+        <v>4.711176936196792</v>
       </c>
       <c r="D2" t="n">
-        <v>29.06246138881657</v>
+        <v>4.722649975682693</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1878997147459902</v>
+        <v>0.03053370364622365</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3173206647296993</v>
+        <v>0.05156460801857632</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.36765749839532</v>
+        <v>4.772244343489239</v>
       </c>
       <c r="D3" t="n">
-        <v>29.69710271827597</v>
+        <v>4.825779191719845</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1878997147459902</v>
+        <v>0.03053370364622365</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3173206647296993</v>
+        <v>0.05156460801857632</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
